--- a/Result/profitability/3666.xlsx
+++ b/Result/profitability/3666.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.86875</v>
+        <v>-0.8075</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.517499999999999</v>
+        <v>-8.135</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.99</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.02125</v>
+        <v>-0.85625</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.0075</v>
+        <v>-8.44</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.97</v>
+        <v>-0.9037499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-5.748749999999999</v>
+        <v>-7.508749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.14375</v>
+        <v>-1.04625</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.506250000000001</v>
+        <v>-5.946249999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-1.04</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.14125</v>
+        <v>-1.1175</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.632499999999999</v>
+        <v>-1.10375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-2.51</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.39625</v>
+        <v>-1.23875</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01625000000000031</v>
+        <v>0.91625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -8556,6 +8556,133 @@
       </c>
       <c r="AM64" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3666</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>151</v>
+      </c>
+      <c r="D65" t="n">
+        <v>164</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-14</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-48</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-31.89%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>10</v>
+      </c>
+      <c r="J65" t="n">
+        <v>-38</v>
+      </c>
+      <c r="K65" t="n">
+        <v>-38</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="M65" t="n">
+        <v>-0.8662500000000001</v>
+      </c>
+      <c r="N65" t="n">
+        <v>-9.481249999999999</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>1</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="X65" t="n">
+        <v>-0.2999999999999999</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>-0.5067531064289573</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.7358490566037736</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>4.479999999999999</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>-0.3291697281410727</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
